--- a/JsonConverter/ExcelFiles/WorkStatData.xlsx
+++ b/JsonConverter/ExcelFiles/WorkStatData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>스탯 id</t>
   </si>
@@ -164,10 +164,13 @@
     <t>EnergyRecoverRate</t>
   </si>
   <si>
-    <t>에너지 회복량</t>
-  </si>
-  <si>
-    <t>회복 주기당 지급량</t>
+    <t>에너지 회복 속도</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>회복 속도 배율. 높을수록 회복 주기가 짧아짐 (반올림 없이 적용)</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -566,51 +569,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -619,49 +577,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -789,7 +704,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -801,34 +716,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -913,18 +828,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,273 +1377,319 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="8" max="8" width="49.1481481481481" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:8">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
+      <c r="E4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="5">
         <v>0</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
+      <c r="E5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="5">
         <v>0</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="E6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="5">
         <v>0</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="E7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="5">
         <v>60</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10">
+      <c r="E8" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="5">
         <v>0.3</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="5">
         <v>3</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="5">
         <v>1</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
+      <c r="E9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="5">
         <v>1</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="5">
         <v>10</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10" t="s">
+      <c r="F10" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="5">
         <v>10</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10">
+      <c r="E11" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="5">
         <v>0.5</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10" t="s">
+      <c r="G11" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="10">
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
-        <v>46</v>
+      <c r="E12" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
